--- a/docs/demo-import/题库导入_生物_演示.xlsx
+++ b/docs/demo-import/题库导入_生物_演示.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题目检查" sheetId="1" r:id="R470badf1b6234918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R7358f3f01d624533"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题目检查" sheetId="1" r:id="Rdbcd59990fe841c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Ra26fc88213b94ccf"/>
   </x:sheets>
 </x:workbook>
 </file>
